--- a/Employee_Reports_wi52/Mohomed Minnas Mohomed Ramees Q0582.xlsx
+++ b/Employee_Reports_wi52/Mohomed Minnas Mohomed Ramees Q0582.xlsx
@@ -37,7 +37,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,12 +54,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
         <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFACD"/>
-        <bgColor rgb="00FFFACD"/>
       </patternFill>
     </fill>
   </fills>
@@ -81,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -93,9 +87,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -475,7 +466,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -578,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>699</v>
+        <v>691</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>707</v>
+        <v>699</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +912,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>714</v>
+        <v>706</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +961,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1007,11 +998,11 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-385</v>
+        <v>-393</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1056,11 +1047,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1105,11 +1096,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1154,11 +1145,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1203,11 +1194,11 @@
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1218,41 +1209,41 @@
       <c r="K16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>IS0 55001 (Other Trainings)</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>03-Sep-2024</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>03-Sep-2026</t>
-        </is>
-      </c>
-      <c r="H17" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
-        <is>
-          <t>19-Aug-2026</t>
-        </is>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
-        <is>
-          <t>EXPIRING SOON</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr"/>
+      <c r="D17" s="3" t="inlineStr"/>
+      <c r="E17" s="3" t="inlineStr"/>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>24-Aug-2026</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>23-Aug-2028</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>726</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>27-Aug-2026</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
